--- a/docs/通信协议.xlsx
+++ b/docs/通信协议.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\document\s_dc\system_design_and_compute_final_project\system_design_and_compute_final_project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBAFB16-77FB-4595-A3FD-69BA551448AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF35350-7379-4A18-BD4A-39A61D87A077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="核心总线通信协议详细内容" sheetId="2" r:id="rId1"/>
@@ -435,10 +435,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -756,13 +756,13 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -774,15 +774,15 @@
       <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <f>SUM(E2:E4)</f>
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
@@ -792,12 +792,12 @@
       <c r="F3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
@@ -807,16 +807,16 @@
       <c r="F4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -828,15 +828,15 @@
       <c r="F5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <f>SUM(E5:E8)</f>
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="3" t="s">
         <v>4</v>
       </c>
@@ -846,12 +846,12 @@
       <c r="F6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="6"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="3" t="s">
         <v>4</v>
       </c>
@@ -861,12 +861,12 @@
       <c r="F7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="6"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
@@ -876,16 +876,16 @@
       <c r="F8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -897,15 +897,15 @@
       <c r="F9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="6">
         <f>SUM(E9:E18)</f>
         <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
       <c r="D10" s="2" t="s">
         <v>2</v>
       </c>
@@ -915,12 +915,12 @@
       <c r="F10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
       <c r="D11" s="2" t="s">
         <v>4</v>
       </c>
@@ -930,12 +930,12 @@
       <c r="F11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
       <c r="D12" s="2" t="s">
         <v>4</v>
       </c>
@@ -945,12 +945,12 @@
       <c r="F12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
       <c r="D13" s="2" t="s">
         <v>4</v>
       </c>
@@ -960,12 +960,12 @@
       <c r="F13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
       <c r="D14" s="2" t="s">
         <v>4</v>
       </c>
@@ -975,12 +975,12 @@
       <c r="F14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
       <c r="D15" s="2" t="s">
         <v>4</v>
       </c>
@@ -990,12 +990,12 @@
       <c r="F15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
       <c r="D16" s="2" t="s">
         <v>3</v>
       </c>
@@ -1005,12 +1005,12 @@
       <c r="F16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
       <c r="D17" s="2" t="s">
         <v>3</v>
       </c>
@@ -1020,12 +1020,12 @@
       <c r="F17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
       <c r="D18" s="2" t="s">
         <v>3</v>
       </c>
@@ -1035,16 +1035,16 @@
       <c r="F18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>41</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -1056,25 +1056,25 @@
       <c r="F19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <f>SUM(E19:E20)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
       <c r="D20" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E20" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="6"/>
+      <c r="G20" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/docs/通信协议.xlsx
+++ b/docs/通信协议.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\document\s_dc\system_design_and_compute_final_project\system_design_and_compute_final_project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF35350-7379-4A18-BD4A-39A61D87A077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEED60D-5A26-48E6-93AE-8F6B4E73A140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="核心总线通信协议详细内容" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
   <si>
     <t>内容结构组成</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -336,6 +336,22 @@
   </si>
   <si>
     <t>control_info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>舵机控制指令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>servo_info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>舵机角度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -435,10 +451,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -721,18 +737,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C59A38-F5DA-4937-B515-B556A2EADA2A}">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="22" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="142.625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.625" style="1"/>
+    <col min="4" max="5" width="12.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="142.58203125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -755,14 +771,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -774,15 +790,15 @@
       <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <f>SUM(E2:E4)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
@@ -792,12 +808,12 @@
       <c r="F3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
@@ -807,16 +823,16 @@
       <c r="F4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>39</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -828,15 +844,15 @@
       <c r="F5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="6">
         <f>SUM(E5:E8)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
       <c r="D6" s="3" t="s">
         <v>4</v>
       </c>
@@ -846,12 +862,12 @@
       <c r="F6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="3" t="s">
         <v>4</v>
       </c>
@@ -861,12 +877,12 @@
       <c r="F7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
@@ -876,16 +892,16 @@
       <c r="F8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -897,15 +913,15 @@
       <c r="F9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <f>SUM(E9:E18)</f>
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="2" t="s">
         <v>2</v>
       </c>
@@ -915,12 +931,12 @@
       <c r="F10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="2" t="s">
         <v>4</v>
       </c>
@@ -930,12 +946,12 @@
       <c r="F11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="2" t="s">
         <v>4</v>
       </c>
@@ -945,12 +961,12 @@
       <c r="F12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="2" t="s">
         <v>4</v>
       </c>
@@ -960,12 +976,12 @@
       <c r="F13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="2" t="s">
         <v>4</v>
       </c>
@@ -975,12 +991,12 @@
       <c r="F14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="2" t="s">
         <v>4</v>
       </c>
@@ -990,12 +1006,12 @@
       <c r="F15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="2" t="s">
         <v>3</v>
       </c>
@@ -1005,12 +1021,12 @@
       <c r="F16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="2" t="s">
         <v>3</v>
       </c>
@@ -1020,12 +1036,12 @@
       <c r="F17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="2" t="s">
         <v>3</v>
       </c>
@@ -1035,16 +1051,16 @@
       <c r="F18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -1056,15 +1072,15 @@
       <c r="F19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="6">
         <f>SUM(E19:E20)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
       <c r="D20" s="3" t="s">
         <v>7</v>
       </c>
@@ -1074,10 +1090,42 @@
       <c r="F20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="5"/>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="2">
+        <v>4</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="2">
+        <f>SUM(E21:E21)</f>
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G9:G18"/>
+    <mergeCell ref="A9:A18"/>
+    <mergeCell ref="B9:B18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C9:C18"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="G2:G4"/>
@@ -1086,14 +1134,6 @@
     <mergeCell ref="G5:G8"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C5:C8"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G9:G18"/>
-    <mergeCell ref="A9:A18"/>
-    <mergeCell ref="B9:B18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C9:C18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
